--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N83_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N83_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.254085750203425</v>
+        <v>0.6912889344080567</v>
       </c>
       <c r="D2" t="n">
-        <v>4.677434602821048</v>
+        <v>0.7600831229584203</v>
       </c>
       <c r="E2" t="n">
-        <v>10.99854342907458</v>
+        <v>1.78726330722462</v>
       </c>
       <c r="F2" t="n">
-        <v>10.7201577540781</v>
+        <v>1.742025635037691</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.25117260835259</v>
+        <v>4.265815548857296</v>
       </c>
       <c r="D3" t="n">
-        <v>26.11775011097724</v>
+        <v>4.244134393033802</v>
       </c>
       <c r="E3" t="n">
-        <v>10.99854342907458</v>
+        <v>1.78726330722462</v>
       </c>
       <c r="F3" t="n">
-        <v>10.7201577540781</v>
+        <v>1.742025635037691</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
